--- a/prova_real/Midas_Lab_ProvaReal_Compilado.xlsx
+++ b/prova_real/Midas_Lab_ProvaReal_Compilado.xlsx
@@ -524,29 +524,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27 → 2026-05-29</t>
+          <t>2026-03-04 → 2026-06-03</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>85.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>114274.29</v>
+        <v>116611.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14274.29</v>
+        <v>16611.43</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14.27</v>
+        <v>16.61</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.44</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>114270</v>
+        <v>116610</v>
       </c>
     </row>
     <row r="3">
@@ -568,29 +568,29 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20 → 2024-02-21</t>
+          <t>2023-11-23 → 2024-02-26</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>90.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>115805.72</v>
+        <v>118106.11</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>15805.72</v>
+        <v>18106.11</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15.81</v>
+        <v>18.11</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.44</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>132336.09</v>
+        <v>137728.07</v>
       </c>
     </row>
     <row r="4">
@@ -612,29 +612,29 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2025-11-24 → 2026-02-26</t>
+          <t>2025-11-27 → 2026-03-03</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>126104.83</v>
+        <v>115812.31</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>26104.83</v>
+        <v>15812.31</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>26.1</v>
+        <v>15.81</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3.44</v>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>166875.81</v>
+        <v>159502.88</v>
       </c>
     </row>
     <row r="5">
@@ -656,14 +656,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26 → 2025-11-21</t>
+          <t>2025-08-29 → 2025-11-26</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>97.8</v>
@@ -672,13 +672,13 @@
         <v>100000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>120149.37</v>
+        <v>121776.01</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20149.37</v>
+        <v>21776.01</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.15</v>
+        <v>21.78</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>3.44</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>200501.28</v>
+        <v>194242.61</v>
       </c>
     </row>
     <row r="6">
@@ -700,29 +700,29 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28 → 2025-08-25</t>
+          <t>2025-06-02 → 2025-08-28</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>87.5</v>
+        <v>88.2</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>114258.75</v>
+        <v>111894.12</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14258.75</v>
+        <v>11894.12</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14.26</v>
+        <v>11.89</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>3.44</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>229092.76</v>
+        <v>217338.05</v>
       </c>
     </row>
     <row r="7">
@@ -744,29 +744,29 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2023-05-05 → 2025-05-27</t>
+          <t>2023-05-05 → 2025-05-30</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>116247.78</v>
+        <v>117253</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>16247.78</v>
+        <v>17253</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.44</v>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>266320.34</v>
+        <v>254828.87</v>
       </c>
     </row>
     <row r="8">
@@ -788,11 +788,11 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19 → 2025-02-20</t>
+          <t>2024-11-25 → 2025-02-25</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>11</v>
@@ -804,24 +804,24 @@
         <v>100000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>103964.55</v>
+        <v>102352.72</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3964.55</v>
+        <v>2352.72</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3.96</v>
+        <v>2.35</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>3.44</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>276866.62</v>
+        <v>260817.34</v>
       </c>
     </row>
     <row r="9">
@@ -832,40 +832,40 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2024-08-21 → 2024-11-18</t>
+          <t>2024-08-26 → 2024-11-22</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>101966.66</v>
+        <v>116070</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1966.66</v>
+        <v>16070</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.97</v>
+        <v>16.07</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3.44</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>282320.89</v>
+        <v>302730.69</v>
       </c>
     </row>
     <row r="10">
@@ -876,29 +876,29 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2024-05-23 → 2024-08-20</t>
+          <t>2024-05-28 → 2024-08-23</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>120227.06</v>
+        <v>120242.87</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>20227.06</v>
+        <v>20242.87</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.23</v>
+        <v>20.24</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>3.44</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>339434.41</v>
+        <v>364003.38</v>
       </c>
     </row>
     <row r="11">
@@ -920,40 +920,40 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22 → 2024-05-22</t>
+          <t>2024-02-27 → 2024-05-27</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>46</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>100000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>93990</v>
+        <v>116488</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>-6010</v>
+        <v>16488</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-6.01</v>
+        <v>16.49</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.44</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>319034.4</v>
+        <v>424027.54</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +971,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>12.7</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="3">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9.26</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="5">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>84</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>319034.4</v>
+        <v>424027.54</v>
       </c>
     </row>
     <row r="9">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>219.03</v>
+        <v>324.03</v>
       </c>
     </row>
     <row r="10">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>184.66</v>
+        <v>289.65</v>
       </c>
     </row>
   </sheetData>
